--- a/data/costs_inputs.xlsx
+++ b/data/costs_inputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aheller\Dropbox\CS\3 - Current Projects\TEA-CART again\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://camsys-my.sharepoint.com/personal/slarue_camsys_com/Documents/Documents/idot_github_puller/TEACART/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E22C64-131E-4930-8175-8BCF00AD5634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{89E22C64-131E-4930-8175-8BCF00AD5634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17615332-3D82-41DF-AFC3-E322215F5E5F}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="11" xr2:uid="{4F0DFC77-7701-46A8-8503-EA1475D00596}"/>
+    <workbookView xWindow="270" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{4F0DFC77-7701-46A8-8503-EA1475D00596}"/>
   </bookViews>
   <sheets>
     <sheet name="bikeped" sheetId="1" r:id="rId1"/>
@@ -240,9 +240,6 @@
     <t>New roundabouts</t>
   </si>
   <si>
-    <t>Medium and Heavy Duty Vehicle Replacement (Electrification)</t>
-  </si>
-  <si>
     <t>Operating Cost per mile</t>
   </si>
   <si>
@@ -355,6 +352,9 @@
   </si>
   <si>
     <t>Annual Maintenance Cost Per Lane-Mile</t>
+  </si>
+  <si>
+    <t>Medium- and Heavy-Duty Vehicle Replacement (Electrification)</t>
   </si>
 </sst>
 </file>
@@ -410,9 +410,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -450,7 +450,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -556,7 +556,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -698,7 +698,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -707,18 +707,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEAFFEE1-34EB-45A0-BDAE-1817B108C539}">
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="35.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -732,7 +732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -746,7 +746,7 @@
         <v>43000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -760,7 +760,7 @@
         <v>43000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -774,7 +774,7 @@
         <v>43000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -788,7 +788,7 @@
         <v>43000</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -802,7 +802,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -816,7 +816,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -830,7 +830,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -844,7 +844,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -858,7 +858,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -872,7 +872,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -886,7 +886,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -900,7 +900,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -914,7 +914,7 @@
         <v>33792</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -928,7 +928,7 @@
         <v>33792</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -942,7 +942,7 @@
         <v>33792</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -956,7 +956,7 @@
         <v>33792</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -970,7 +970,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -984,7 +984,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -998,7 +998,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>11742.720000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -1034,16 +1034,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82596B3-442F-491C-96CE-C1DAF95D51FE}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>73</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
@@ -1052,12 +1052,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
         <v>74</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
       </c>
       <c r="C3">
         <v>8200</v>
@@ -1071,33 +1071,33 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{950AA5B9-78AB-451F-83C1-232F88063E66}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
       </c>
       <c r="C2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" t="s">
         <v>80</v>
-      </c>
-      <c r="B3" t="s">
-        <v>81</v>
       </c>
       <c r="C3">
         <v>938</v>
@@ -1106,12 +1106,12 @@
         <v>3090</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4">
         <v>28401</v>
@@ -1120,12 +1120,12 @@
         <v>26964</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5">
         <v>75000</v>
@@ -1134,12 +1134,12 @@
         <v>28312</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6">
         <v>28401</v>
@@ -1148,12 +1148,12 @@
         <v>26964</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7">
         <v>140000</v>
@@ -1162,12 +1162,12 @@
         <v>39097</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8">
         <v>50000</v>
@@ -1176,12 +1176,12 @@
         <v>39097</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>28401</v>
@@ -1198,14 +1198,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85675AB6-01BE-4A22-A141-3AAB62579551}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1213,15 +1213,15 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>89</v>
-      </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>90</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -1233,9 +1233,9 @@
         <v>397184.66800000006</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1247,9 +1247,9 @@
         <v>278535.72850000003</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -1261,9 +1261,9 @@
         <v>327580.94</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -1283,14 +1283,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E02B68-A2A2-4102-B2D6-3E913EB2976E}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1301,45 +1301,45 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C3">
         <v>3.4649999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C4">
         <v>3.8809999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" t="s">
         <v>94</v>
-      </c>
-      <c r="B5" t="s">
-        <v>95</v>
       </c>
       <c r="C5">
         <v>0.1148</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" t="s">
         <v>96</v>
-      </c>
-      <c r="B6" t="s">
-        <v>97</v>
       </c>
       <c r="C6">
         <v>2.54</v>
@@ -1353,14 +1353,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A41E7B3-2994-4315-846B-EBF73DD83E2A}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1371,12 +1371,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
         <v>99</v>
-      </c>
-      <c r="B3" t="s">
-        <v>100</v>
       </c>
       <c r="C3">
         <v>1000000</v>
@@ -1390,21 +1390,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBBD329-8E42-4F9D-98BB-7699CC68C825}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>0.70316123608534298</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>0.70316123608534298</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>0.57269119769119758</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>0.57269119769119758</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>0.22944967090526897</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>0.22944967090526897</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1548,14 +1548,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA2F69F1-E6CF-42D3-9FD5-8CB19A5213C3}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>0.44197515446533014</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>0.44197515446533014</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>0.3599861767971585</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>0.3599861767971585</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>0.1300214801796524</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1682,14 +1682,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A785AFAA-AA4E-4D91-AD9D-571962B14F8E}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -1719,14 +1719,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA7508C-6A8F-4C7A-BF0C-DB9BB4467772}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1756,14 +1756,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7660CE48-BCC7-4D4F-8378-0D9F9B49303B}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>1.7782540748068197E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>3.2571058992039076E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>1.1884709668099125</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -1856,14 +1856,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE96978-AA77-447A-AE8E-10413262DA71}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -1893,20 +1893,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32922511-C8E2-4940-B2AC-62EBC45529AC}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>56</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>375000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -1972,55 +1972,55 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACE3CB9-FD42-4AC2-99DA-1355F549B789}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" t="s">
         <v>65</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
         <v>67</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
       </c>
       <c r="C3">
         <v>42100</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4">
         <v>49000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
         <v>44</v>
@@ -2029,9 +2029,9 @@
         <v>49000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
@@ -2040,9 +2040,9 @@
         <v>175000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
@@ -2051,9 +2051,9 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
@@ -2062,9 +2062,9 @@
         <v>67000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
@@ -2073,9 +2073,9 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
         <v>41</v>
@@ -2084,9 +2084,9 @@
         <v>316000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
         <v>41</v>
